--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗЕМЕДЕЛСКА ТЕХНИКА ООД/ЗЕМЕДЕЛСКА ТЕХНИКА ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗЕМЕДЕЛСКА ТЕХНИКА ООД/ЗЕМЕДЕЛСКА ТЕХНИКА ООД.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="ЗЕМЕДЕЛСКА ТЕХНИКА ООД" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="52">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -70,28 +73,85 @@
     <t>2026-05-15</t>
   </si>
   <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1156 Добрич бул. Добруджа</t>
+  </si>
+  <si>
     <t>ТХ6051МТ</t>
   </si>
   <si>
+    <t>ЗТ1</t>
+  </si>
+  <si>
     <t>78970153027720688</t>
   </si>
   <si>
+    <t>78970153027720696</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>16:09</t>
-  </si>
-  <si>
-    <t>10:47</t>
-  </si>
-  <si>
-    <t>10:41</t>
-  </si>
-  <si>
-    <t>08:16</t>
-  </si>
-  <si>
-    <t>09:14</t>
+    <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>16:09:00</t>
+  </si>
+  <si>
+    <t>10:47:00</t>
+  </si>
+  <si>
+    <t>10:41:00</t>
+  </si>
+  <si>
+    <t>08:15:00</t>
+  </si>
+  <si>
+    <t>09:14:00</t>
+  </si>
+  <si>
+    <t>18:18:00</t>
+  </si>
+  <si>
+    <t>07:51:00</t>
+  </si>
+  <si>
+    <t>20:58:00</t>
+  </si>
+  <si>
+    <t>3231303701 3231303701</t>
+  </si>
+  <si>
+    <t>3231380447 3231380447</t>
+  </si>
+  <si>
+    <t>3231556714 3231556714</t>
+  </si>
+  <si>
+    <t>3231789809 3231789809</t>
+  </si>
+  <si>
+    <t>3231933368 3231933368</t>
+  </si>
+  <si>
+    <t>3232209753 3232209753</t>
+  </si>
+  <si>
+    <t>3232400213 3232400213</t>
+  </si>
+  <si>
+    <t>3232540304 3232540304</t>
   </si>
   <si>
     <t>Общи литри по продукт / ЗЕМЕДЕЛСКА ТЕХНИКА ООД</t>
@@ -515,24 +575,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -572,283 +634,453 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1156</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F2">
         <v>30.38</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2">
         <v>1.43</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>43.44</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.52</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>46.18</v>
       </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>78051</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1156</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F3">
         <v>32.42</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3">
         <v>1.43</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>46.36</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.52</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>49.28</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>78316</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4">
-        <v>1156</v>
-      </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F4">
         <v>38.04</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4">
         <v>1.43</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>54.4</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.53</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>58.2</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
         <v>23</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>78967</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5">
-        <v>1156</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F5">
         <v>27.66</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5">
         <v>1.47</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>40.66</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.54</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>42.6</v>
       </c>
-      <c r="K5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5">
+      <c r="L5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="M5">
-        <v>79895</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6">
-        <v>1156</v>
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F6">
         <v>31.04</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6">
         <v>1.48</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>45.94</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.54</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>47.8</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c r="L6">
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7">
+        <v>29.54</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7">
+        <v>1.5</v>
+      </c>
+      <c r="I7" s="1">
+        <v>44.31</v>
+      </c>
+      <c r="J7">
+        <v>1.57</v>
+      </c>
+      <c r="K7" s="1">
+        <v>46.38</v>
+      </c>
+      <c r="L7" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="M6">
-        <v>80585</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="3" t="s">
+      <c r="N7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8">
+        <v>31.62</v>
+      </c>
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8">
+        <v>1.5</v>
+      </c>
+      <c r="I8" s="1">
+        <v>47.43</v>
+      </c>
+      <c r="J8">
+        <v>1.57</v>
+      </c>
+      <c r="K8" s="1">
+        <v>49.64</v>
+      </c>
+      <c r="L8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="4" t="s">
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9">
+        <v>54</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9">
+        <v>1.63</v>
+      </c>
+      <c r="I9" s="1">
+        <v>88.02</v>
+      </c>
+      <c r="J9">
+        <v>1.71</v>
+      </c>
+      <c r="K9" s="1">
+        <v>92.34</v>
+      </c>
+      <c r="L9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B14" s="6">
+        <v>220.7</v>
+      </c>
+      <c r="C14" s="6">
+        <v>7</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1.4614</v>
+      </c>
+      <c r="E14" s="6">
+        <v>322.54</v>
+      </c>
+      <c r="F14" s="6">
+        <v>340.08</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="6">
-        <v>159.54</v>
-      </c>
-      <c r="C11" s="6">
-        <v>5</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.4467</v>
-      </c>
-      <c r="E11" s="6">
-        <v>230.8</v>
-      </c>
-      <c r="F11" s="6">
-        <v>244.06</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="9">
-        <v>159.54</v>
-      </c>
-      <c r="C12" s="9">
-        <v>5</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="9">
-        <v>230.8</v>
-      </c>
-      <c r="F12" s="9">
-        <v>244.06</v>
+      <c r="B15" s="6">
+        <v>54</v>
+      </c>
+      <c r="C15" s="6">
+        <v>1</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1.63</v>
+      </c>
+      <c r="E15" s="6">
+        <v>88.02</v>
+      </c>
+      <c r="F15" s="6">
+        <v>92.34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="9">
+        <v>274.7</v>
+      </c>
+      <c r="C16" s="9">
+        <v>8</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="9">
+        <v>410.56</v>
+      </c>
+      <c r="F16" s="9">
+        <v>432.42</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗЕМЕДЕЛСКА ТЕХНИКА ООД/ЗЕМЕДЕЛСКА ТЕХНИКА ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗЕМЕДЕЛСКА ТЕХНИКА ООД/ЗЕМЕДЕЛСКА ТЕХНИКА ООД.xlsx
@@ -205,7 +205,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -215,12 +215,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -270,17 +264,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗЕМЕДЕЛСКА ТЕХНИКА ООД/ЗЕМЕДЕЛСКА ТЕХНИКА ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗЕМЕДЕЛСКА ТЕХНИКА ООД/ЗЕМЕДЕЛСКА ТЕХНИКА ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="51">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -70,7 +79,7 @@
     <t>2026-06-21</t>
   </si>
   <si>
-    <t>Добрич Добруджа</t>
+    <t>1156 Добрич бул. Добруджа</t>
   </si>
   <si>
     <t>ТХ6051МТ</t>
@@ -97,25 +106,49 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-06-01 20:39:20</t>
-  </si>
-  <si>
-    <t>2026-06-03 08:43:05</t>
-  </si>
-  <si>
-    <t>2026-06-07 10:22:11</t>
-  </si>
-  <si>
-    <t>2026-06-11 18:16:55</t>
-  </si>
-  <si>
-    <t>2026-06-12 19:55:42</t>
-  </si>
-  <si>
-    <t>2026-06-18 08:59:15</t>
-  </si>
-  <si>
-    <t>2026-06-21 09:44:44</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>20:39:00</t>
+  </si>
+  <si>
+    <t>08:42:00</t>
+  </si>
+  <si>
+    <t>10:22:00</t>
+  </si>
+  <si>
+    <t>18:16:00</t>
+  </si>
+  <si>
+    <t>19:55:00</t>
+  </si>
+  <si>
+    <t>08:58:00</t>
+  </si>
+  <si>
+    <t>09:44:00</t>
+  </si>
+  <si>
+    <t>3232732410 3232732410</t>
+  </si>
+  <si>
+    <t>3232816065 3232816065</t>
+  </si>
+  <si>
+    <t>3233011748 3233011748</t>
+  </si>
+  <si>
+    <t>3233210181 3233210181</t>
+  </si>
+  <si>
+    <t>3233267114 3233267114</t>
+  </si>
+  <si>
+    <t>3233535087 3233535087</t>
+  </si>
+  <si>
+    <t>3233687360 3233687360</t>
   </si>
   <si>
     <t>Общи литри по продукт / ЗЕМЕДЕЛСКА ТЕХНИКА ООД</t>
@@ -533,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -542,14 +575,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -583,255 +619,327 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>39.97</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2">
         <v>1.52</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>60.75</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.57</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>62.75</v>
       </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F3">
         <v>50.3</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3">
         <v>1.6</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>80.48</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.69</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>85.01000000000001</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
       </c>
       <c r="F4">
         <v>37.88</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4">
         <v>1.5</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>56.82</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.56</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>59.09</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
       </c>
       <c r="F5">
         <v>64.40000000000001</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5">
         <v>1.55</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>99.81999999999999</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.62</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>104.33</v>
       </c>
-      <c r="K5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F6">
         <v>39.99</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6">
         <v>1.48</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>59.19</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.56</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>62.38</v>
       </c>
-      <c r="K6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F7">
         <v>27.58</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7">
         <v>1.46</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>40.27</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.55</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>42.75</v>
       </c>
-      <c r="K7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7">
+        <v>176134</v>
+      </c>
+      <c r="N7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F8">
         <v>36.29</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8">
         <v>1.43</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>51.89</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.53</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>55.52</v>
       </c>
-      <c r="K8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -839,29 +947,29 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:14">
       <c r="A12" s="4" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B13" s="6">
         <v>181.71</v>
@@ -879,9 +987,9 @@
         <v>282.49</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:14">
       <c r="A14" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B14" s="6">
         <v>114.7</v>
@@ -899,9 +1007,9 @@
         <v>189.34</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:14">
       <c r="A15" s="8" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B15" s="9">
         <v>296.41</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗЕМЕДЕЛСКА ТЕХНИКА ООД/ЗЕМЕДЕЛСКА ТЕХНИКА ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗЕМЕДЕЛСКА ТЕХНИКА ООД/ЗЕМЕДЕЛСКА ТЕХНИКА ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,13 +55,22 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-10</t>
   </si>
   <si>
     <t>2026-07-15</t>
   </si>
   <si>
-    <t>Добрич Добруджа</t>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>1156 Добрич бул. Добруджа</t>
   </si>
   <si>
     <t>ТХ6051МТ</t>
@@ -70,10 +82,31 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-07-10 08:47:06</t>
-  </si>
-  <si>
-    <t>2026-07-15 07:12:57</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>08:47:00</t>
+  </si>
+  <si>
+    <t>07:12:00</t>
+  </si>
+  <si>
+    <t>12:31:00</t>
+  </si>
+  <si>
+    <t>20:56:00</t>
+  </si>
+  <si>
+    <t>3234585819 3234585819</t>
+  </si>
+  <si>
+    <t>3234807078 3234807078</t>
+  </si>
+  <si>
+    <t>3235250210 3235250210</t>
+  </si>
+  <si>
+    <t>3235544255 3235544255</t>
   </si>
   <si>
     <t>Общи литри по продукт / ЗЕМЕДЕЛСКА ТЕХНИКА ООД</t>
@@ -491,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -500,15 +533,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -545,154 +580,260 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>33.14</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2">
         <v>1.39</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>46.06</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.49</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>49.38</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>29.33</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3">
         <v>1.4</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>41.06</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.49</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>43.7</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="L3">
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4">
+        <v>33.31</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4">
+        <v>1.44</v>
+      </c>
+      <c r="I4" s="1">
+        <v>47.97</v>
+      </c>
+      <c r="J4">
+        <v>1.52</v>
+      </c>
+      <c r="K4" s="1">
+        <v>50.63</v>
+      </c>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
+      <c r="N4" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="3" t="s">
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5">
+        <v>1.49</v>
+      </c>
+      <c r="I5" s="1">
+        <v>50.66</v>
+      </c>
+      <c r="J5">
+        <v>1.54</v>
+      </c>
+      <c r="K5" s="1">
+        <v>52.36</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:14">
+      <c r="A8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>9</v>
+      <c r="B10" s="6">
+        <v>129.78</v>
+      </c>
+      <c r="C10" s="6">
+        <v>4</v>
+      </c>
+      <c r="D10" s="7">
+        <v>1.4313</v>
+      </c>
+      <c r="E10" s="6">
+        <v>185.75</v>
+      </c>
+      <c r="F10" s="6">
+        <v>196.07</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="6">
-        <v>62.47</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1.3946</v>
-      </c>
-      <c r="E8" s="6">
-        <v>87.12</v>
-      </c>
-      <c r="F8" s="6">
-        <v>93.08</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="9">
-        <v>62.47</v>
-      </c>
-      <c r="C9" s="9">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="9">
-        <v>87.12</v>
-      </c>
-      <c r="F9" s="9">
-        <v>93.08</v>
+    <row r="11" spans="1:14">
+      <c r="A11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="9">
+        <v>129.78</v>
+      </c>
+      <c r="C11" s="9">
+        <v>4</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="9">
+        <v>185.75</v>
+      </c>
+      <c r="F11" s="9">
+        <v>196.07</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗЕМЕДЕЛСКА ТЕХНИКА ООД/ЗЕМЕДЕЛСКА ТЕХНИКА ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗЕМЕДЕЛСКА ТЕХНИКА ООД/ЗЕМЕДЕЛСКА ТЕХНИКА ООД.xlsx
@@ -133,7 +133,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -804,7 +804,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="7">
-        <v>1.4313</v>
+        <v>1.431268</v>
       </c>
       <c r="E10" s="6">
         <v>185.75</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗЕМЕДЕЛСКА ТЕХНИКА ООД/ЗЕМЕДЕЛСКА ТЕХНИКА ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗЕМЕДЕЛСКА ТЕХНИКА ООД/ЗЕМЕДЕЛСКА ТЕХНИКА ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="38">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -524,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -537,13 +540,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -586,186 +589,201 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2">
+        <v>33.141</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2">
+        <v>1.359</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.389</v>
+      </c>
+      <c r="J2">
+        <v>46.032849</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="L2" s="1">
+        <v>49.38009</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3">
+        <v>29.329</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3">
+        <v>1.369</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.399</v>
+      </c>
+      <c r="J3">
+        <v>41.031271</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="L3" s="1">
+        <v>43.70021</v>
+      </c>
+      <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>33.309</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4">
+        <v>1.401</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.441</v>
+      </c>
+      <c r="J4">
+        <v>47.998269</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L4" s="1">
+        <v>50.62968</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="F2">
-        <v>33.14</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E5" t="s">
         <v>22</v>
-      </c>
-      <c r="H2">
-        <v>1.39</v>
-      </c>
-      <c r="I2" s="1">
-        <v>46.06</v>
-      </c>
-      <c r="J2">
-        <v>1.49</v>
-      </c>
-      <c r="K2" s="1">
-        <v>49.38</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>29.33</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3">
-        <v>1.4</v>
-      </c>
-      <c r="I3" s="1">
-        <v>41.06</v>
-      </c>
-      <c r="J3">
-        <v>1.49</v>
-      </c>
-      <c r="K3" s="1">
-        <v>43.7</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4">
-        <v>33.31</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4">
-        <v>1.44</v>
-      </c>
-      <c r="I4" s="1">
-        <v>47.97</v>
-      </c>
-      <c r="J4">
-        <v>1.52</v>
-      </c>
-      <c r="K4" s="1">
-        <v>50.63</v>
-      </c>
-      <c r="L4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
       </c>
       <c r="F5">
         <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H5">
-        <v>1.49</v>
+        <v>1.449</v>
       </c>
       <c r="I5" s="1">
-        <v>50.66</v>
+        <v>1.489</v>
       </c>
       <c r="J5">
+        <v>50.626</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.54</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>52.36</v>
       </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5">
+      <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>30</v>
+      <c r="O5" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -773,59 +791,59 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" s="6">
-        <v>129.78</v>
+        <v>129.779</v>
       </c>
       <c r="C10" s="6">
         <v>4</v>
       </c>
       <c r="D10" s="7">
-        <v>1.431268</v>
+        <v>1.430805</v>
       </c>
       <c r="E10" s="6">
-        <v>185.75</v>
+        <v>185.69</v>
       </c>
       <c r="F10" s="6">
         <v>196.07</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" s="9">
-        <v>129.78</v>
+        <v>129.779</v>
       </c>
       <c r="C11" s="9">
         <v>4</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="9">
-        <v>185.75</v>
+        <v>185.69</v>
       </c>
       <c r="F11" s="9">
         <v>196.07</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗЕМЕДЕЛСКА ТЕХНИКА ООД/ЗЕМЕДЕЛСКА ТЕХНИКА ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЗЕМЕДЕЛСКА ТЕХНИКА ООД/ЗЕМЕДЕЛСКА ТЕХНИКА ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -135,8 +132,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -229,10 +226,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -527,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -540,13 +537,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -589,201 +586,186 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
       </c>
       <c r="F2">
         <v>33.141</v>
       </c>
       <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2">
+        <v>1.389</v>
+      </c>
+      <c r="I2" s="1">
+        <v>46.033</v>
+      </c>
+      <c r="J2">
+        <v>1.49</v>
+      </c>
+      <c r="K2" s="1">
+        <v>49.38</v>
+      </c>
+      <c r="L2" t="s">
         <v>23</v>
       </c>
-      <c r="H2">
-        <v>1.359</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.389</v>
-      </c>
-      <c r="J2">
-        <v>46.032849</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L2" s="1">
-        <v>49.38009</v>
-      </c>
-      <c r="M2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>28</v>
+      <c r="N2" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
       </c>
       <c r="F3">
         <v>29.329</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H3">
-        <v>1.369</v>
+        <v>1.399</v>
       </c>
       <c r="I3" s="1">
-        <v>1.399</v>
+        <v>41.031</v>
       </c>
       <c r="J3">
-        <v>41.031271</v>
+        <v>1.49</v>
       </c>
       <c r="K3" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L3" s="1">
-        <v>43.70021</v>
-      </c>
-      <c r="M3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3">
+        <v>43.7</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>29</v>
+      <c r="N3" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
       </c>
       <c r="F4">
         <v>33.309</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4">
-        <v>1.401</v>
+        <v>1.441</v>
       </c>
       <c r="I4" s="1">
-        <v>1.441</v>
+        <v>47.998</v>
       </c>
       <c r="J4">
-        <v>47.998269</v>
+        <v>1.52</v>
       </c>
       <c r="K4" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L4" s="1">
-        <v>50.62968</v>
-      </c>
-      <c r="M4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4">
+        <v>50.63</v>
+      </c>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>30</v>
+      <c r="N4" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
       </c>
       <c r="F5">
         <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5">
-        <v>1.449</v>
+        <v>1.489</v>
       </c>
       <c r="I5" s="1">
-        <v>1.489</v>
+        <v>50.626</v>
       </c>
       <c r="J5">
-        <v>50.626</v>
+        <v>1.54</v>
       </c>
       <c r="K5" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L5" s="1">
         <v>52.36</v>
       </c>
-      <c r="M5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5">
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="3" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -791,49 +773,49 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="E9" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:14">
       <c r="A10" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="6">
         <v>129.779</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="7">
         <v>4</v>
       </c>
       <c r="D10" s="7">
-        <v>1.430805</v>
-      </c>
-      <c r="E10" s="6">
-        <v>185.69</v>
-      </c>
-      <c r="F10" s="6">
+        <v>1.431</v>
+      </c>
+      <c r="E10" s="7">
+        <v>185.688</v>
+      </c>
+      <c r="F10" s="7">
         <v>196.07</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14">
       <c r="A11" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="9">
         <v>129.779</v>
@@ -843,7 +825,7 @@
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="9">
-        <v>185.69</v>
+        <v>185.688</v>
       </c>
       <c r="F11" s="9">
         <v>196.07</v>
